--- a/Data/EC/NIT-9007865127.xlsx
+++ b/Data/EC/NIT-9007865127.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96920AD7-114D-4CB0-93EE-4F38DEA98052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A5B1B81-DEB2-4FD9-82AD-4996C448F501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{FA362747-86C4-4B3A-B2D3-E571B534F0F0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{87093070-B97F-43BB-9F19-9E5F064501B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -752,22 +752,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DE103EA-F157-68EF-F17F-8CEEC1DDD837}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0D7AB8E-A643-FABE-9A80-66BF26DFAC11}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -776,7 +776,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -789,7 +789,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1118,23 +1118,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7100DA92-BB34-467F-94C6-57BBC5CE2C3C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1D27FB-9504-455E-92CE-DD34EAEC24A2}">
   <dimension ref="B2:J489"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.46484375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -1147,7 +1147,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1158,7 +1158,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1169,7 +1169,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1180,8 +1180,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>106</v>
       </c>
@@ -1196,8 +1196,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1212,8 +1212,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>107</v>
       </c>
@@ -1228,8 +1228,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>108</v>
       </c>
@@ -1248,7 +1248,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1300,7 +1300,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1323,7 +1323,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1346,7 +1346,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1369,7 +1369,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1392,7 +1392,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1415,7 +1415,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1438,7 +1438,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1461,7 +1461,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1484,7 +1484,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1507,7 +1507,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1530,7 +1530,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1553,7 +1553,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1576,7 +1576,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1599,7 +1599,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1622,7 +1622,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1645,7 +1645,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1668,7 +1668,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1691,7 +1691,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1714,7 +1714,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1737,7 +1737,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1760,7 +1760,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1783,7 +1783,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1806,7 +1806,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1829,7 +1829,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1852,7 +1852,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1875,7 +1875,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1898,7 +1898,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1921,7 +1921,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1944,7 +1944,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1967,7 +1967,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1990,7 +1990,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -2013,7 +2013,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -2036,7 +2036,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -2059,7 +2059,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -2082,7 +2082,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2105,7 +2105,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2128,7 +2128,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2151,7 +2151,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2174,7 +2174,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2197,7 +2197,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2220,7 +2220,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2243,7 +2243,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2266,7 +2266,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2289,7 +2289,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2312,7 +2312,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2335,7 +2335,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2358,7 +2358,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2381,7 +2381,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2404,7 +2404,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2427,7 +2427,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2450,7 +2450,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2473,7 +2473,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2496,7 +2496,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2519,7 +2519,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2542,7 +2542,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2565,7 +2565,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2588,7 +2588,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2611,7 +2611,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2634,7 +2634,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2657,7 +2657,7 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
@@ -2680,7 +2680,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2703,7 +2703,7 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
@@ -2726,7 +2726,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2749,7 +2749,7 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
@@ -2772,7 +2772,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2795,7 +2795,7 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
@@ -2818,7 +2818,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2841,7 +2841,7 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
@@ -2864,7 +2864,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
@@ -2887,7 +2887,7 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
@@ -2910,7 +2910,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
@@ -2933,7 +2933,7 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
@@ -2956,7 +2956,7 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
@@ -2979,7 +2979,7 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
@@ -3002,7 +3002,7 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
@@ -3025,7 +3025,7 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
@@ -3048,7 +3048,7 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
@@ -3071,7 +3071,7 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
@@ -3094,7 +3094,7 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
@@ -3117,7 +3117,7 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
@@ -3140,7 +3140,7 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
         <v>8</v>
       </c>
@@ -3163,7 +3163,7 @@
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
         <v>8</v>
       </c>
@@ -3186,7 +3186,7 @@
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
         <v>8</v>
       </c>
@@ -3209,7 +3209,7 @@
       <c r="I99" s="19"/>
       <c r="J99" s="20"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
         <v>8</v>
       </c>
@@ -3232,7 +3232,7 @@
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
         <v>8</v>
       </c>
@@ -3255,7 +3255,7 @@
       <c r="I101" s="19"/>
       <c r="J101" s="20"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
         <v>8</v>
       </c>
@@ -3278,7 +3278,7 @@
       <c r="I102" s="19"/>
       <c r="J102" s="20"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
         <v>8</v>
       </c>
@@ -3301,7 +3301,7 @@
       <c r="I103" s="19"/>
       <c r="J103" s="20"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="15" t="s">
         <v>8</v>
       </c>
@@ -3324,7 +3324,7 @@
       <c r="I104" s="19"/>
       <c r="J104" s="20"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="15" t="s">
         <v>8</v>
       </c>
@@ -3347,7 +3347,7 @@
       <c r="I105" s="19"/>
       <c r="J105" s="20"/>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" s="15" t="s">
         <v>8</v>
       </c>
@@ -3370,7 +3370,7 @@
       <c r="I106" s="19"/>
       <c r="J106" s="20"/>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B107" s="15" t="s">
         <v>8</v>
       </c>
@@ -3393,7 +3393,7 @@
       <c r="I107" s="19"/>
       <c r="J107" s="20"/>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B108" s="15" t="s">
         <v>8</v>
       </c>
@@ -3416,7 +3416,7 @@
       <c r="I108" s="19"/>
       <c r="J108" s="20"/>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B109" s="15" t="s">
         <v>8</v>
       </c>
@@ -3439,7 +3439,7 @@
       <c r="I109" s="19"/>
       <c r="J109" s="20"/>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B110" s="15" t="s">
         <v>8</v>
       </c>
@@ -3462,7 +3462,7 @@
       <c r="I110" s="19"/>
       <c r="J110" s="20"/>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B111" s="15" t="s">
         <v>8</v>
       </c>
@@ -3485,7 +3485,7 @@
       <c r="I111" s="19"/>
       <c r="J111" s="20"/>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B112" s="15" t="s">
         <v>8</v>
       </c>
@@ -3508,7 +3508,7 @@
       <c r="I112" s="19"/>
       <c r="J112" s="20"/>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B113" s="15" t="s">
         <v>8</v>
       </c>
@@ -3531,7 +3531,7 @@
       <c r="I113" s="19"/>
       <c r="J113" s="20"/>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B114" s="15" t="s">
         <v>8</v>
       </c>
@@ -3554,7 +3554,7 @@
       <c r="I114" s="19"/>
       <c r="J114" s="20"/>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B115" s="15" t="s">
         <v>8</v>
       </c>
@@ -3577,7 +3577,7 @@
       <c r="I115" s="19"/>
       <c r="J115" s="20"/>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B116" s="15" t="s">
         <v>8</v>
       </c>
@@ -3600,7 +3600,7 @@
       <c r="I116" s="19"/>
       <c r="J116" s="20"/>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B117" s="15" t="s">
         <v>8</v>
       </c>
@@ -3623,7 +3623,7 @@
       <c r="I117" s="19"/>
       <c r="J117" s="20"/>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B118" s="15" t="s">
         <v>8</v>
       </c>
@@ -3646,7 +3646,7 @@
       <c r="I118" s="19"/>
       <c r="J118" s="20"/>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B119" s="15" t="s">
         <v>8</v>
       </c>
@@ -3669,7 +3669,7 @@
       <c r="I119" s="19"/>
       <c r="J119" s="20"/>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B120" s="15" t="s">
         <v>8</v>
       </c>
@@ -3692,7 +3692,7 @@
       <c r="I120" s="19"/>
       <c r="J120" s="20"/>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B121" s="15" t="s">
         <v>8</v>
       </c>
@@ -3715,7 +3715,7 @@
       <c r="I121" s="19"/>
       <c r="J121" s="20"/>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B122" s="15" t="s">
         <v>8</v>
       </c>
@@ -3738,7 +3738,7 @@
       <c r="I122" s="19"/>
       <c r="J122" s="20"/>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B123" s="15" t="s">
         <v>8</v>
       </c>
@@ -3761,7 +3761,7 @@
       <c r="I123" s="19"/>
       <c r="J123" s="20"/>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B124" s="15" t="s">
         <v>8</v>
       </c>
@@ -3784,7 +3784,7 @@
       <c r="I124" s="19"/>
       <c r="J124" s="20"/>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B125" s="15" t="s">
         <v>8</v>
       </c>
@@ -3807,7 +3807,7 @@
       <c r="I125" s="19"/>
       <c r="J125" s="20"/>
     </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B126" s="15" t="s">
         <v>8</v>
       </c>
@@ -3830,7 +3830,7 @@
       <c r="I126" s="19"/>
       <c r="J126" s="20"/>
     </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B127" s="15" t="s">
         <v>8</v>
       </c>
@@ -3853,7 +3853,7 @@
       <c r="I127" s="19"/>
       <c r="J127" s="20"/>
     </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="128" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B128" s="15" t="s">
         <v>8</v>
       </c>
@@ -3876,7 +3876,7 @@
       <c r="I128" s="19"/>
       <c r="J128" s="20"/>
     </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="129" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B129" s="15" t="s">
         <v>8</v>
       </c>
@@ -3899,7 +3899,7 @@
       <c r="I129" s="19"/>
       <c r="J129" s="20"/>
     </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B130" s="15" t="s">
         <v>8</v>
       </c>
@@ -3922,7 +3922,7 @@
       <c r="I130" s="19"/>
       <c r="J130" s="20"/>
     </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="131" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B131" s="15" t="s">
         <v>8</v>
       </c>
@@ -3945,7 +3945,7 @@
       <c r="I131" s="19"/>
       <c r="J131" s="20"/>
     </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="132" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B132" s="15" t="s">
         <v>8</v>
       </c>
@@ -3968,7 +3968,7 @@
       <c r="I132" s="19"/>
       <c r="J132" s="20"/>
     </row>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="133" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B133" s="15" t="s">
         <v>8</v>
       </c>
@@ -3991,7 +3991,7 @@
       <c r="I133" s="19"/>
       <c r="J133" s="20"/>
     </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="134" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B134" s="15" t="s">
         <v>8</v>
       </c>
@@ -4014,7 +4014,7 @@
       <c r="I134" s="19"/>
       <c r="J134" s="20"/>
     </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="135" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B135" s="15" t="s">
         <v>8</v>
       </c>
@@ -4037,7 +4037,7 @@
       <c r="I135" s="19"/>
       <c r="J135" s="20"/>
     </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="136" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B136" s="15" t="s">
         <v>8</v>
       </c>
@@ -4060,7 +4060,7 @@
       <c r="I136" s="19"/>
       <c r="J136" s="20"/>
     </row>
-    <row r="137" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="137" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B137" s="15" t="s">
         <v>8</v>
       </c>
@@ -4083,7 +4083,7 @@
       <c r="I137" s="19"/>
       <c r="J137" s="20"/>
     </row>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="138" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B138" s="15" t="s">
         <v>8</v>
       </c>
@@ -4106,7 +4106,7 @@
       <c r="I138" s="19"/>
       <c r="J138" s="20"/>
     </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="139" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B139" s="15" t="s">
         <v>8</v>
       </c>
@@ -4129,7 +4129,7 @@
       <c r="I139" s="19"/>
       <c r="J139" s="20"/>
     </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="140" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B140" s="15" t="s">
         <v>8</v>
       </c>
@@ -4152,7 +4152,7 @@
       <c r="I140" s="19"/>
       <c r="J140" s="20"/>
     </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="141" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B141" s="15" t="s">
         <v>8</v>
       </c>
@@ -4175,7 +4175,7 @@
       <c r="I141" s="19"/>
       <c r="J141" s="20"/>
     </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="142" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B142" s="15" t="s">
         <v>8</v>
       </c>
@@ -4198,7 +4198,7 @@
       <c r="I142" s="19"/>
       <c r="J142" s="20"/>
     </row>
-    <row r="143" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="143" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B143" s="15" t="s">
         <v>8</v>
       </c>
@@ -4221,7 +4221,7 @@
       <c r="I143" s="19"/>
       <c r="J143" s="20"/>
     </row>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="144" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B144" s="15" t="s">
         <v>8</v>
       </c>
@@ -4244,7 +4244,7 @@
       <c r="I144" s="19"/>
       <c r="J144" s="20"/>
     </row>
-    <row r="145" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B145" s="15" t="s">
         <v>8</v>
       </c>
@@ -4267,7 +4267,7 @@
       <c r="I145" s="19"/>
       <c r="J145" s="20"/>
     </row>
-    <row r="146" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="146" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B146" s="15" t="s">
         <v>8</v>
       </c>
@@ -4290,7 +4290,7 @@
       <c r="I146" s="19"/>
       <c r="J146" s="20"/>
     </row>
-    <row r="147" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="147" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B147" s="15" t="s">
         <v>8</v>
       </c>
@@ -4313,7 +4313,7 @@
       <c r="I147" s="19"/>
       <c r="J147" s="20"/>
     </row>
-    <row r="148" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="148" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B148" s="15" t="s">
         <v>8</v>
       </c>
@@ -4336,7 +4336,7 @@
       <c r="I148" s="19"/>
       <c r="J148" s="20"/>
     </row>
-    <row r="149" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="149" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B149" s="15" t="s">
         <v>8</v>
       </c>
@@ -4359,7 +4359,7 @@
       <c r="I149" s="19"/>
       <c r="J149" s="20"/>
     </row>
-    <row r="150" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="150" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B150" s="15" t="s">
         <v>8</v>
       </c>
@@ -4382,7 +4382,7 @@
       <c r="I150" s="19"/>
       <c r="J150" s="20"/>
     </row>
-    <row r="151" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="151" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B151" s="15" t="s">
         <v>8</v>
       </c>
@@ -4405,7 +4405,7 @@
       <c r="I151" s="19"/>
       <c r="J151" s="20"/>
     </row>
-    <row r="152" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="152" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B152" s="15" t="s">
         <v>8</v>
       </c>
@@ -4428,7 +4428,7 @@
       <c r="I152" s="19"/>
       <c r="J152" s="20"/>
     </row>
-    <row r="153" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="153" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B153" s="15" t="s">
         <v>8</v>
       </c>
@@ -4451,7 +4451,7 @@
       <c r="I153" s="19"/>
       <c r="J153" s="20"/>
     </row>
-    <row r="154" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="154" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B154" s="15" t="s">
         <v>8</v>
       </c>
@@ -4474,7 +4474,7 @@
       <c r="I154" s="19"/>
       <c r="J154" s="20"/>
     </row>
-    <row r="155" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="155" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B155" s="15" t="s">
         <v>8</v>
       </c>
@@ -4497,7 +4497,7 @@
       <c r="I155" s="19"/>
       <c r="J155" s="20"/>
     </row>
-    <row r="156" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="156" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B156" s="15" t="s">
         <v>8</v>
       </c>
@@ -4520,7 +4520,7 @@
       <c r="I156" s="19"/>
       <c r="J156" s="20"/>
     </row>
-    <row r="157" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="157" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B157" s="15" t="s">
         <v>8</v>
       </c>
@@ -4543,7 +4543,7 @@
       <c r="I157" s="19"/>
       <c r="J157" s="20"/>
     </row>
-    <row r="158" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="158" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B158" s="15" t="s">
         <v>8</v>
       </c>
@@ -4566,7 +4566,7 @@
       <c r="I158" s="19"/>
       <c r="J158" s="20"/>
     </row>
-    <row r="159" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="159" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B159" s="15" t="s">
         <v>8</v>
       </c>
@@ -4589,7 +4589,7 @@
       <c r="I159" s="19"/>
       <c r="J159" s="20"/>
     </row>
-    <row r="160" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="160" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B160" s="15" t="s">
         <v>8</v>
       </c>
@@ -4612,7 +4612,7 @@
       <c r="I160" s="19"/>
       <c r="J160" s="20"/>
     </row>
-    <row r="161" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="161" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B161" s="15" t="s">
         <v>8</v>
       </c>
@@ -4635,7 +4635,7 @@
       <c r="I161" s="19"/>
       <c r="J161" s="20"/>
     </row>
-    <row r="162" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="162" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B162" s="15" t="s">
         <v>8</v>
       </c>
@@ -4658,7 +4658,7 @@
       <c r="I162" s="19"/>
       <c r="J162" s="20"/>
     </row>
-    <row r="163" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="163" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B163" s="15" t="s">
         <v>8</v>
       </c>
@@ -4681,7 +4681,7 @@
       <c r="I163" s="19"/>
       <c r="J163" s="20"/>
     </row>
-    <row r="164" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="164" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B164" s="15" t="s">
         <v>8</v>
       </c>
@@ -4704,7 +4704,7 @@
       <c r="I164" s="19"/>
       <c r="J164" s="20"/>
     </row>
-    <row r="165" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="165" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B165" s="15" t="s">
         <v>8</v>
       </c>
@@ -4727,7 +4727,7 @@
       <c r="I165" s="19"/>
       <c r="J165" s="20"/>
     </row>
-    <row r="166" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="166" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B166" s="15" t="s">
         <v>8</v>
       </c>
@@ -4750,7 +4750,7 @@
       <c r="I166" s="19"/>
       <c r="J166" s="20"/>
     </row>
-    <row r="167" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="167" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B167" s="15" t="s">
         <v>8</v>
       </c>
@@ -4773,7 +4773,7 @@
       <c r="I167" s="19"/>
       <c r="J167" s="20"/>
     </row>
-    <row r="168" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="168" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B168" s="15" t="s">
         <v>8</v>
       </c>
@@ -4796,7 +4796,7 @@
       <c r="I168" s="19"/>
       <c r="J168" s="20"/>
     </row>
-    <row r="169" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="169" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B169" s="15" t="s">
         <v>8</v>
       </c>
@@ -4819,7 +4819,7 @@
       <c r="I169" s="19"/>
       <c r="J169" s="20"/>
     </row>
-    <row r="170" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="170" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B170" s="15" t="s">
         <v>8</v>
       </c>
@@ -4842,7 +4842,7 @@
       <c r="I170" s="19"/>
       <c r="J170" s="20"/>
     </row>
-    <row r="171" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="171" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B171" s="15" t="s">
         <v>8</v>
       </c>
@@ -4865,7 +4865,7 @@
       <c r="I171" s="19"/>
       <c r="J171" s="20"/>
     </row>
-    <row r="172" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="172" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B172" s="15" t="s">
         <v>8</v>
       </c>
@@ -4888,7 +4888,7 @@
       <c r="I172" s="19"/>
       <c r="J172" s="20"/>
     </row>
-    <row r="173" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="173" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B173" s="15" t="s">
         <v>8</v>
       </c>
@@ -4911,7 +4911,7 @@
       <c r="I173" s="19"/>
       <c r="J173" s="20"/>
     </row>
-    <row r="174" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="174" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B174" s="15" t="s">
         <v>8</v>
       </c>
@@ -4934,7 +4934,7 @@
       <c r="I174" s="19"/>
       <c r="J174" s="20"/>
     </row>
-    <row r="175" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="175" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B175" s="15" t="s">
         <v>8</v>
       </c>
@@ -4957,7 +4957,7 @@
       <c r="I175" s="19"/>
       <c r="J175" s="20"/>
     </row>
-    <row r="176" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="176" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B176" s="15" t="s">
         <v>8</v>
       </c>
@@ -4980,7 +4980,7 @@
       <c r="I176" s="19"/>
       <c r="J176" s="20"/>
     </row>
-    <row r="177" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="177" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B177" s="15" t="s">
         <v>8</v>
       </c>
@@ -5003,7 +5003,7 @@
       <c r="I177" s="19"/>
       <c r="J177" s="20"/>
     </row>
-    <row r="178" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="178" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B178" s="15" t="s">
         <v>8</v>
       </c>
@@ -5026,7 +5026,7 @@
       <c r="I178" s="19"/>
       <c r="J178" s="20"/>
     </row>
-    <row r="179" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="179" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B179" s="15" t="s">
         <v>8</v>
       </c>
@@ -5049,7 +5049,7 @@
       <c r="I179" s="19"/>
       <c r="J179" s="20"/>
     </row>
-    <row r="180" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="180" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B180" s="15" t="s">
         <v>8</v>
       </c>
@@ -5072,7 +5072,7 @@
       <c r="I180" s="19"/>
       <c r="J180" s="20"/>
     </row>
-    <row r="181" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="181" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B181" s="15" t="s">
         <v>8</v>
       </c>
@@ -5095,7 +5095,7 @@
       <c r="I181" s="19"/>
       <c r="J181" s="20"/>
     </row>
-    <row r="182" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="182" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B182" s="15" t="s">
         <v>8</v>
       </c>
@@ -5118,7 +5118,7 @@
       <c r="I182" s="19"/>
       <c r="J182" s="20"/>
     </row>
-    <row r="183" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="183" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B183" s="15" t="s">
         <v>8</v>
       </c>
@@ -5141,7 +5141,7 @@
       <c r="I183" s="19"/>
       <c r="J183" s="20"/>
     </row>
-    <row r="184" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="184" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B184" s="15" t="s">
         <v>8</v>
       </c>
@@ -5164,7 +5164,7 @@
       <c r="I184" s="19"/>
       <c r="J184" s="20"/>
     </row>
-    <row r="185" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="185" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B185" s="15" t="s">
         <v>8</v>
       </c>
@@ -5187,7 +5187,7 @@
       <c r="I185" s="19"/>
       <c r="J185" s="20"/>
     </row>
-    <row r="186" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="186" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B186" s="15" t="s">
         <v>8</v>
       </c>
@@ -5210,7 +5210,7 @@
       <c r="I186" s="19"/>
       <c r="J186" s="20"/>
     </row>
-    <row r="187" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="187" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B187" s="15" t="s">
         <v>8</v>
       </c>
@@ -5233,7 +5233,7 @@
       <c r="I187" s="19"/>
       <c r="J187" s="20"/>
     </row>
-    <row r="188" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="188" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B188" s="15" t="s">
         <v>8</v>
       </c>
@@ -5256,7 +5256,7 @@
       <c r="I188" s="19"/>
       <c r="J188" s="20"/>
     </row>
-    <row r="189" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="189" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B189" s="15" t="s">
         <v>8</v>
       </c>
@@ -5279,7 +5279,7 @@
       <c r="I189" s="19"/>
       <c r="J189" s="20"/>
     </row>
-    <row r="190" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="190" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B190" s="15" t="s">
         <v>8</v>
       </c>
@@ -5302,7 +5302,7 @@
       <c r="I190" s="19"/>
       <c r="J190" s="20"/>
     </row>
-    <row r="191" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="191" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B191" s="15" t="s">
         <v>8</v>
       </c>
@@ -5325,7 +5325,7 @@
       <c r="I191" s="19"/>
       <c r="J191" s="20"/>
     </row>
-    <row r="192" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="192" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B192" s="15" t="s">
         <v>8</v>
       </c>
@@ -5348,7 +5348,7 @@
       <c r="I192" s="19"/>
       <c r="J192" s="20"/>
     </row>
-    <row r="193" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="193" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B193" s="15" t="s">
         <v>8</v>
       </c>
@@ -5371,7 +5371,7 @@
       <c r="I193" s="19"/>
       <c r="J193" s="20"/>
     </row>
-    <row r="194" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="194" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B194" s="15" t="s">
         <v>8</v>
       </c>
@@ -5394,7 +5394,7 @@
       <c r="I194" s="19"/>
       <c r="J194" s="20"/>
     </row>
-    <row r="195" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="195" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B195" s="15" t="s">
         <v>8</v>
       </c>
@@ -5417,7 +5417,7 @@
       <c r="I195" s="19"/>
       <c r="J195" s="20"/>
     </row>
-    <row r="196" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="196" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B196" s="15" t="s">
         <v>8</v>
       </c>
@@ -5440,7 +5440,7 @@
       <c r="I196" s="19"/>
       <c r="J196" s="20"/>
     </row>
-    <row r="197" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="197" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B197" s="15" t="s">
         <v>8</v>
       </c>
@@ -5463,7 +5463,7 @@
       <c r="I197" s="19"/>
       <c r="J197" s="20"/>
     </row>
-    <row r="198" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="198" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B198" s="15" t="s">
         <v>8</v>
       </c>
@@ -5486,7 +5486,7 @@
       <c r="I198" s="19"/>
       <c r="J198" s="20"/>
     </row>
-    <row r="199" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="199" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B199" s="15" t="s">
         <v>8</v>
       </c>
@@ -5509,7 +5509,7 @@
       <c r="I199" s="19"/>
       <c r="J199" s="20"/>
     </row>
-    <row r="200" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="200" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B200" s="15" t="s">
         <v>8</v>
       </c>
@@ -5532,7 +5532,7 @@
       <c r="I200" s="19"/>
       <c r="J200" s="20"/>
     </row>
-    <row r="201" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="201" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B201" s="15" t="s">
         <v>8</v>
       </c>
@@ -5555,7 +5555,7 @@
       <c r="I201" s="19"/>
       <c r="J201" s="20"/>
     </row>
-    <row r="202" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="202" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B202" s="15" t="s">
         <v>8</v>
       </c>
@@ -5578,7 +5578,7 @@
       <c r="I202" s="19"/>
       <c r="J202" s="20"/>
     </row>
-    <row r="203" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="203" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B203" s="15" t="s">
         <v>8</v>
       </c>
@@ -5601,7 +5601,7 @@
       <c r="I203" s="19"/>
       <c r="J203" s="20"/>
     </row>
-    <row r="204" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="204" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B204" s="15" t="s">
         <v>8</v>
       </c>
@@ -5624,7 +5624,7 @@
       <c r="I204" s="19"/>
       <c r="J204" s="20"/>
     </row>
-    <row r="205" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="205" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B205" s="15" t="s">
         <v>8</v>
       </c>
@@ -5647,7 +5647,7 @@
       <c r="I205" s="19"/>
       <c r="J205" s="20"/>
     </row>
-    <row r="206" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="206" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B206" s="15" t="s">
         <v>8</v>
       </c>
@@ -5670,7 +5670,7 @@
       <c r="I206" s="19"/>
       <c r="J206" s="20"/>
     </row>
-    <row r="207" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="207" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B207" s="15" t="s">
         <v>8</v>
       </c>
@@ -5693,7 +5693,7 @@
       <c r="I207" s="19"/>
       <c r="J207" s="20"/>
     </row>
-    <row r="208" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="208" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B208" s="15" t="s">
         <v>8</v>
       </c>
@@ -5716,7 +5716,7 @@
       <c r="I208" s="19"/>
       <c r="J208" s="20"/>
     </row>
-    <row r="209" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="209" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B209" s="15" t="s">
         <v>8</v>
       </c>
@@ -5739,7 +5739,7 @@
       <c r="I209" s="19"/>
       <c r="J209" s="20"/>
     </row>
-    <row r="210" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="210" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B210" s="15" t="s">
         <v>8</v>
       </c>
@@ -5762,7 +5762,7 @@
       <c r="I210" s="19"/>
       <c r="J210" s="20"/>
     </row>
-    <row r="211" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="211" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B211" s="15" t="s">
         <v>8</v>
       </c>
@@ -5785,7 +5785,7 @@
       <c r="I211" s="19"/>
       <c r="J211" s="20"/>
     </row>
-    <row r="212" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="212" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B212" s="15" t="s">
         <v>8</v>
       </c>
@@ -5808,7 +5808,7 @@
       <c r="I212" s="19"/>
       <c r="J212" s="20"/>
     </row>
-    <row r="213" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="213" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B213" s="15" t="s">
         <v>8</v>
       </c>
@@ -5831,7 +5831,7 @@
       <c r="I213" s="19"/>
       <c r="J213" s="20"/>
     </row>
-    <row r="214" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="214" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B214" s="15" t="s">
         <v>8</v>
       </c>
@@ -5854,7 +5854,7 @@
       <c r="I214" s="19"/>
       <c r="J214" s="20"/>
     </row>
-    <row r="215" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="215" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B215" s="15" t="s">
         <v>8</v>
       </c>
@@ -5877,7 +5877,7 @@
       <c r="I215" s="19"/>
       <c r="J215" s="20"/>
     </row>
-    <row r="216" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="216" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B216" s="15" t="s">
         <v>8</v>
       </c>
@@ -5900,7 +5900,7 @@
       <c r="I216" s="19"/>
       <c r="J216" s="20"/>
     </row>
-    <row r="217" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="217" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B217" s="15" t="s">
         <v>8</v>
       </c>
@@ -5923,7 +5923,7 @@
       <c r="I217" s="19"/>
       <c r="J217" s="20"/>
     </row>
-    <row r="218" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="218" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B218" s="15" t="s">
         <v>8</v>
       </c>
@@ -5946,7 +5946,7 @@
       <c r="I218" s="19"/>
       <c r="J218" s="20"/>
     </row>
-    <row r="219" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="219" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B219" s="15" t="s">
         <v>8</v>
       </c>
@@ -5969,7 +5969,7 @@
       <c r="I219" s="19"/>
       <c r="J219" s="20"/>
     </row>
-    <row r="220" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="220" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B220" s="15" t="s">
         <v>8</v>
       </c>
@@ -5992,7 +5992,7 @@
       <c r="I220" s="19"/>
       <c r="J220" s="20"/>
     </row>
-    <row r="221" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="221" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B221" s="15" t="s">
         <v>8</v>
       </c>
@@ -6015,7 +6015,7 @@
       <c r="I221" s="19"/>
       <c r="J221" s="20"/>
     </row>
-    <row r="222" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="222" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B222" s="15" t="s">
         <v>8</v>
       </c>
@@ -6038,7 +6038,7 @@
       <c r="I222" s="19"/>
       <c r="J222" s="20"/>
     </row>
-    <row r="223" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="223" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B223" s="15" t="s">
         <v>8</v>
       </c>
@@ -6061,7 +6061,7 @@
       <c r="I223" s="19"/>
       <c r="J223" s="20"/>
     </row>
-    <row r="224" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="224" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B224" s="15" t="s">
         <v>8</v>
       </c>
@@ -6084,7 +6084,7 @@
       <c r="I224" s="19"/>
       <c r="J224" s="20"/>
     </row>
-    <row r="225" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="225" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B225" s="15" t="s">
         <v>8</v>
       </c>
@@ -6107,7 +6107,7 @@
       <c r="I225" s="19"/>
       <c r="J225" s="20"/>
     </row>
-    <row r="226" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="226" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B226" s="15" t="s">
         <v>8</v>
       </c>
@@ -6130,7 +6130,7 @@
       <c r="I226" s="19"/>
       <c r="J226" s="20"/>
     </row>
-    <row r="227" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="227" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B227" s="15" t="s">
         <v>8</v>
       </c>
@@ -6153,7 +6153,7 @@
       <c r="I227" s="19"/>
       <c r="J227" s="20"/>
     </row>
-    <row r="228" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="228" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B228" s="15" t="s">
         <v>8</v>
       </c>
@@ -6176,7 +6176,7 @@
       <c r="I228" s="19"/>
       <c r="J228" s="20"/>
     </row>
-    <row r="229" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="229" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B229" s="15" t="s">
         <v>8</v>
       </c>
@@ -6199,7 +6199,7 @@
       <c r="I229" s="19"/>
       <c r="J229" s="20"/>
     </row>
-    <row r="230" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="230" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B230" s="15" t="s">
         <v>8</v>
       </c>
@@ -6222,7 +6222,7 @@
       <c r="I230" s="19"/>
       <c r="J230" s="20"/>
     </row>
-    <row r="231" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="231" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B231" s="15" t="s">
         <v>8</v>
       </c>
@@ -6245,7 +6245,7 @@
       <c r="I231" s="19"/>
       <c r="J231" s="20"/>
     </row>
-    <row r="232" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="232" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B232" s="15" t="s">
         <v>8</v>
       </c>
@@ -6268,7 +6268,7 @@
       <c r="I232" s="19"/>
       <c r="J232" s="20"/>
     </row>
-    <row r="233" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="233" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B233" s="15" t="s">
         <v>8</v>
       </c>
@@ -6291,7 +6291,7 @@
       <c r="I233" s="19"/>
       <c r="J233" s="20"/>
     </row>
-    <row r="234" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="234" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B234" s="15" t="s">
         <v>8</v>
       </c>
@@ -6314,7 +6314,7 @@
       <c r="I234" s="19"/>
       <c r="J234" s="20"/>
     </row>
-    <row r="235" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="235" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B235" s="15" t="s">
         <v>8</v>
       </c>
@@ -6337,7 +6337,7 @@
       <c r="I235" s="19"/>
       <c r="J235" s="20"/>
     </row>
-    <row r="236" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="236" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B236" s="15" t="s">
         <v>8</v>
       </c>
@@ -6360,7 +6360,7 @@
       <c r="I236" s="19"/>
       <c r="J236" s="20"/>
     </row>
-    <row r="237" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="237" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B237" s="15" t="s">
         <v>8</v>
       </c>
@@ -6383,7 +6383,7 @@
       <c r="I237" s="19"/>
       <c r="J237" s="20"/>
     </row>
-    <row r="238" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="238" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B238" s="15" t="s">
         <v>8</v>
       </c>
@@ -6406,7 +6406,7 @@
       <c r="I238" s="19"/>
       <c r="J238" s="20"/>
     </row>
-    <row r="239" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="239" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B239" s="15" t="s">
         <v>8</v>
       </c>
@@ -6429,7 +6429,7 @@
       <c r="I239" s="19"/>
       <c r="J239" s="20"/>
     </row>
-    <row r="240" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="240" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B240" s="15" t="s">
         <v>8</v>
       </c>
@@ -6452,7 +6452,7 @@
       <c r="I240" s="19"/>
       <c r="J240" s="20"/>
     </row>
-    <row r="241" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="241" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B241" s="15" t="s">
         <v>8</v>
       </c>
@@ -6475,7 +6475,7 @@
       <c r="I241" s="19"/>
       <c r="J241" s="20"/>
     </row>
-    <row r="242" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="242" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B242" s="15" t="s">
         <v>8</v>
       </c>
@@ -6498,7 +6498,7 @@
       <c r="I242" s="19"/>
       <c r="J242" s="20"/>
     </row>
-    <row r="243" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="243" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B243" s="15" t="s">
         <v>8</v>
       </c>
@@ -6521,7 +6521,7 @@
       <c r="I243" s="19"/>
       <c r="J243" s="20"/>
     </row>
-    <row r="244" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="244" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B244" s="15" t="s">
         <v>8</v>
       </c>
@@ -6544,7 +6544,7 @@
       <c r="I244" s="19"/>
       <c r="J244" s="20"/>
     </row>
-    <row r="245" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="245" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B245" s="15" t="s">
         <v>8</v>
       </c>
@@ -6567,7 +6567,7 @@
       <c r="I245" s="19"/>
       <c r="J245" s="20"/>
     </row>
-    <row r="246" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="246" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B246" s="15" t="s">
         <v>8</v>
       </c>
@@ -6590,7 +6590,7 @@
       <c r="I246" s="19"/>
       <c r="J246" s="20"/>
     </row>
-    <row r="247" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="247" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B247" s="15" t="s">
         <v>8</v>
       </c>
@@ -6613,7 +6613,7 @@
       <c r="I247" s="19"/>
       <c r="J247" s="20"/>
     </row>
-    <row r="248" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="248" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B248" s="15" t="s">
         <v>8</v>
       </c>
@@ -6636,7 +6636,7 @@
       <c r="I248" s="19"/>
       <c r="J248" s="20"/>
     </row>
-    <row r="249" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="249" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B249" s="15" t="s">
         <v>8</v>
       </c>
@@ -6659,7 +6659,7 @@
       <c r="I249" s="19"/>
       <c r="J249" s="20"/>
     </row>
-    <row r="250" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="250" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B250" s="15" t="s">
         <v>8</v>
       </c>
@@ -6682,7 +6682,7 @@
       <c r="I250" s="19"/>
       <c r="J250" s="20"/>
     </row>
-    <row r="251" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="251" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B251" s="15" t="s">
         <v>8</v>
       </c>
@@ -6705,7 +6705,7 @@
       <c r="I251" s="19"/>
       <c r="J251" s="20"/>
     </row>
-    <row r="252" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="252" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B252" s="15" t="s">
         <v>8</v>
       </c>
@@ -6728,7 +6728,7 @@
       <c r="I252" s="19"/>
       <c r="J252" s="20"/>
     </row>
-    <row r="253" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="253" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B253" s="15" t="s">
         <v>8</v>
       </c>
@@ -6751,7 +6751,7 @@
       <c r="I253" s="19"/>
       <c r="J253" s="20"/>
     </row>
-    <row r="254" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="254" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B254" s="15" t="s">
         <v>8</v>
       </c>
@@ -6774,7 +6774,7 @@
       <c r="I254" s="19"/>
       <c r="J254" s="20"/>
     </row>
-    <row r="255" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="255" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B255" s="15" t="s">
         <v>8</v>
       </c>
@@ -6797,7 +6797,7 @@
       <c r="I255" s="19"/>
       <c r="J255" s="20"/>
     </row>
-    <row r="256" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="256" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B256" s="15" t="s">
         <v>8</v>
       </c>
@@ -6820,7 +6820,7 @@
       <c r="I256" s="19"/>
       <c r="J256" s="20"/>
     </row>
-    <row r="257" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="257" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B257" s="15" t="s">
         <v>8</v>
       </c>
@@ -6843,7 +6843,7 @@
       <c r="I257" s="19"/>
       <c r="J257" s="20"/>
     </row>
-    <row r="258" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="258" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B258" s="15" t="s">
         <v>8</v>
       </c>
@@ -6866,7 +6866,7 @@
       <c r="I258" s="19"/>
       <c r="J258" s="20"/>
     </row>
-    <row r="259" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="259" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B259" s="15" t="s">
         <v>8</v>
       </c>
@@ -6889,7 +6889,7 @@
       <c r="I259" s="19"/>
       <c r="J259" s="20"/>
     </row>
-    <row r="260" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="260" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B260" s="15" t="s">
         <v>8</v>
       </c>
@@ -6912,7 +6912,7 @@
       <c r="I260" s="19"/>
       <c r="J260" s="20"/>
     </row>
-    <row r="261" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="261" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B261" s="15" t="s">
         <v>8</v>
       </c>
@@ -6935,7 +6935,7 @@
       <c r="I261" s="19"/>
       <c r="J261" s="20"/>
     </row>
-    <row r="262" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="262" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B262" s="15" t="s">
         <v>8</v>
       </c>
@@ -6958,7 +6958,7 @@
       <c r="I262" s="19"/>
       <c r="J262" s="20"/>
     </row>
-    <row r="263" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="263" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B263" s="15" t="s">
         <v>8</v>
       </c>
@@ -6981,7 +6981,7 @@
       <c r="I263" s="19"/>
       <c r="J263" s="20"/>
     </row>
-    <row r="264" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="264" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B264" s="15" t="s">
         <v>8</v>
       </c>
@@ -7004,7 +7004,7 @@
       <c r="I264" s="19"/>
       <c r="J264" s="20"/>
     </row>
-    <row r="265" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="265" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B265" s="15" t="s">
         <v>8</v>
       </c>
@@ -7027,7 +7027,7 @@
       <c r="I265" s="19"/>
       <c r="J265" s="20"/>
     </row>
-    <row r="266" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="266" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B266" s="15" t="s">
         <v>8</v>
       </c>
@@ -7050,7 +7050,7 @@
       <c r="I266" s="19"/>
       <c r="J266" s="20"/>
     </row>
-    <row r="267" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="267" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B267" s="15" t="s">
         <v>8</v>
       </c>
@@ -7073,7 +7073,7 @@
       <c r="I267" s="19"/>
       <c r="J267" s="20"/>
     </row>
-    <row r="268" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="268" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B268" s="15" t="s">
         <v>8</v>
       </c>
@@ -7096,7 +7096,7 @@
       <c r="I268" s="19"/>
       <c r="J268" s="20"/>
     </row>
-    <row r="269" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="269" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B269" s="15" t="s">
         <v>8</v>
       </c>
@@ -7119,7 +7119,7 @@
       <c r="I269" s="19"/>
       <c r="J269" s="20"/>
     </row>
-    <row r="270" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="270" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B270" s="15" t="s">
         <v>8</v>
       </c>
@@ -7142,7 +7142,7 @@
       <c r="I270" s="19"/>
       <c r="J270" s="20"/>
     </row>
-    <row r="271" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="271" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B271" s="15" t="s">
         <v>8</v>
       </c>
@@ -7165,7 +7165,7 @@
       <c r="I271" s="19"/>
       <c r="J271" s="20"/>
     </row>
-    <row r="272" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="272" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B272" s="15" t="s">
         <v>8</v>
       </c>
@@ -7188,7 +7188,7 @@
       <c r="I272" s="19"/>
       <c r="J272" s="20"/>
     </row>
-    <row r="273" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="273" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B273" s="15" t="s">
         <v>8</v>
       </c>
@@ -7211,7 +7211,7 @@
       <c r="I273" s="19"/>
       <c r="J273" s="20"/>
     </row>
-    <row r="274" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="274" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B274" s="15" t="s">
         <v>8</v>
       </c>
@@ -7234,7 +7234,7 @@
       <c r="I274" s="19"/>
       <c r="J274" s="20"/>
     </row>
-    <row r="275" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="275" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B275" s="15" t="s">
         <v>8</v>
       </c>
@@ -7257,7 +7257,7 @@
       <c r="I275" s="19"/>
       <c r="J275" s="20"/>
     </row>
-    <row r="276" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="276" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B276" s="15" t="s">
         <v>8</v>
       </c>
@@ -7280,7 +7280,7 @@
       <c r="I276" s="19"/>
       <c r="J276" s="20"/>
     </row>
-    <row r="277" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="277" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B277" s="15" t="s">
         <v>8</v>
       </c>
@@ -7303,7 +7303,7 @@
       <c r="I277" s="19"/>
       <c r="J277" s="20"/>
     </row>
-    <row r="278" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="278" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B278" s="15" t="s">
         <v>8</v>
       </c>
@@ -7326,7 +7326,7 @@
       <c r="I278" s="19"/>
       <c r="J278" s="20"/>
     </row>
-    <row r="279" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="279" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B279" s="15" t="s">
         <v>8</v>
       </c>
@@ -7349,7 +7349,7 @@
       <c r="I279" s="19"/>
       <c r="J279" s="20"/>
     </row>
-    <row r="280" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="280" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B280" s="15" t="s">
         <v>8</v>
       </c>
@@ -7372,7 +7372,7 @@
       <c r="I280" s="19"/>
       <c r="J280" s="20"/>
     </row>
-    <row r="281" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="281" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B281" s="15" t="s">
         <v>8</v>
       </c>
@@ -7395,7 +7395,7 @@
       <c r="I281" s="19"/>
       <c r="J281" s="20"/>
     </row>
-    <row r="282" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="282" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B282" s="15" t="s">
         <v>8</v>
       </c>
@@ -7418,7 +7418,7 @@
       <c r="I282" s="19"/>
       <c r="J282" s="20"/>
     </row>
-    <row r="283" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="283" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B283" s="15" t="s">
         <v>8</v>
       </c>
@@ -7441,7 +7441,7 @@
       <c r="I283" s="19"/>
       <c r="J283" s="20"/>
     </row>
-    <row r="284" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="284" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B284" s="15" t="s">
         <v>8</v>
       </c>
@@ -7464,7 +7464,7 @@
       <c r="I284" s="19"/>
       <c r="J284" s="20"/>
     </row>
-    <row r="285" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="285" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B285" s="15" t="s">
         <v>8</v>
       </c>
@@ -7487,7 +7487,7 @@
       <c r="I285" s="19"/>
       <c r="J285" s="20"/>
     </row>
-    <row r="286" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="286" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B286" s="15" t="s">
         <v>8</v>
       </c>
@@ -7510,7 +7510,7 @@
       <c r="I286" s="19"/>
       <c r="J286" s="20"/>
     </row>
-    <row r="287" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="287" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B287" s="15" t="s">
         <v>8</v>
       </c>
@@ -7533,7 +7533,7 @@
       <c r="I287" s="19"/>
       <c r="J287" s="20"/>
     </row>
-    <row r="288" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="288" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B288" s="15" t="s">
         <v>8</v>
       </c>
@@ -7556,7 +7556,7 @@
       <c r="I288" s="19"/>
       <c r="J288" s="20"/>
     </row>
-    <row r="289" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="289" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B289" s="15" t="s">
         <v>8</v>
       </c>
@@ -7579,7 +7579,7 @@
       <c r="I289" s="19"/>
       <c r="J289" s="20"/>
     </row>
-    <row r="290" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="290" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B290" s="15" t="s">
         <v>8</v>
       </c>
@@ -7602,7 +7602,7 @@
       <c r="I290" s="19"/>
       <c r="J290" s="20"/>
     </row>
-    <row r="291" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="291" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B291" s="15" t="s">
         <v>8</v>
       </c>
@@ -7625,7 +7625,7 @@
       <c r="I291" s="19"/>
       <c r="J291" s="20"/>
     </row>
-    <row r="292" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="292" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B292" s="15" t="s">
         <v>8</v>
       </c>
@@ -7648,7 +7648,7 @@
       <c r="I292" s="19"/>
       <c r="J292" s="20"/>
     </row>
-    <row r="293" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="293" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B293" s="15" t="s">
         <v>8</v>
       </c>
@@ -7671,7 +7671,7 @@
       <c r="I293" s="19"/>
       <c r="J293" s="20"/>
     </row>
-    <row r="294" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="294" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B294" s="15" t="s">
         <v>8</v>
       </c>
@@ -7694,7 +7694,7 @@
       <c r="I294" s="19"/>
       <c r="J294" s="20"/>
     </row>
-    <row r="295" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="295" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B295" s="15" t="s">
         <v>8</v>
       </c>
@@ -7717,7 +7717,7 @@
       <c r="I295" s="19"/>
       <c r="J295" s="20"/>
     </row>
-    <row r="296" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="296" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B296" s="15" t="s">
         <v>8</v>
       </c>
@@ -7740,7 +7740,7 @@
       <c r="I296" s="19"/>
       <c r="J296" s="20"/>
     </row>
-    <row r="297" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="297" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B297" s="15" t="s">
         <v>8</v>
       </c>
@@ -7763,7 +7763,7 @@
       <c r="I297" s="19"/>
       <c r="J297" s="20"/>
     </row>
-    <row r="298" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="298" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B298" s="15" t="s">
         <v>8</v>
       </c>
@@ -7786,7 +7786,7 @@
       <c r="I298" s="19"/>
       <c r="J298" s="20"/>
     </row>
-    <row r="299" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="299" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B299" s="15" t="s">
         <v>8</v>
       </c>
@@ -7809,7 +7809,7 @@
       <c r="I299" s="19"/>
       <c r="J299" s="20"/>
     </row>
-    <row r="300" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="300" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B300" s="15" t="s">
         <v>8</v>
       </c>
@@ -7832,7 +7832,7 @@
       <c r="I300" s="19"/>
       <c r="J300" s="20"/>
     </row>
-    <row r="301" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="301" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B301" s="15" t="s">
         <v>8</v>
       </c>
@@ -7855,7 +7855,7 @@
       <c r="I301" s="19"/>
       <c r="J301" s="20"/>
     </row>
-    <row r="302" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="302" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B302" s="15" t="s">
         <v>8</v>
       </c>
@@ -7878,7 +7878,7 @@
       <c r="I302" s="19"/>
       <c r="J302" s="20"/>
     </row>
-    <row r="303" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="303" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B303" s="15" t="s">
         <v>8</v>
       </c>
@@ -7901,7 +7901,7 @@
       <c r="I303" s="19"/>
       <c r="J303" s="20"/>
     </row>
-    <row r="304" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="304" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B304" s="15" t="s">
         <v>8</v>
       </c>
@@ -7924,7 +7924,7 @@
       <c r="I304" s="19"/>
       <c r="J304" s="20"/>
     </row>
-    <row r="305" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="305" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B305" s="15" t="s">
         <v>8</v>
       </c>
@@ -7947,7 +7947,7 @@
       <c r="I305" s="19"/>
       <c r="J305" s="20"/>
     </row>
-    <row r="306" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="306" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B306" s="15" t="s">
         <v>8</v>
       </c>
@@ -7970,7 +7970,7 @@
       <c r="I306" s="19"/>
       <c r="J306" s="20"/>
     </row>
-    <row r="307" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="307" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B307" s="15" t="s">
         <v>8</v>
       </c>
@@ -7993,7 +7993,7 @@
       <c r="I307" s="19"/>
       <c r="J307" s="20"/>
     </row>
-    <row r="308" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="308" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B308" s="15" t="s">
         <v>8</v>
       </c>
@@ -8016,7 +8016,7 @@
       <c r="I308" s="19"/>
       <c r="J308" s="20"/>
     </row>
-    <row r="309" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="309" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B309" s="15" t="s">
         <v>8</v>
       </c>
@@ -8039,7 +8039,7 @@
       <c r="I309" s="19"/>
       <c r="J309" s="20"/>
     </row>
-    <row r="310" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="310" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B310" s="15" t="s">
         <v>8</v>
       </c>
@@ -8062,7 +8062,7 @@
       <c r="I310" s="19"/>
       <c r="J310" s="20"/>
     </row>
-    <row r="311" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="311" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B311" s="15" t="s">
         <v>8</v>
       </c>
@@ -8085,7 +8085,7 @@
       <c r="I311" s="19"/>
       <c r="J311" s="20"/>
     </row>
-    <row r="312" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="312" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B312" s="15" t="s">
         <v>8</v>
       </c>
@@ -8108,7 +8108,7 @@
       <c r="I312" s="19"/>
       <c r="J312" s="20"/>
     </row>
-    <row r="313" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="313" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B313" s="15" t="s">
         <v>8</v>
       </c>
@@ -8131,7 +8131,7 @@
       <c r="I313" s="19"/>
       <c r="J313" s="20"/>
     </row>
-    <row r="314" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="314" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B314" s="15" t="s">
         <v>8</v>
       </c>
@@ -8154,7 +8154,7 @@
       <c r="I314" s="19"/>
       <c r="J314" s="20"/>
     </row>
-    <row r="315" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="315" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B315" s="15" t="s">
         <v>8</v>
       </c>
@@ -8177,7 +8177,7 @@
       <c r="I315" s="19"/>
       <c r="J315" s="20"/>
     </row>
-    <row r="316" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="316" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B316" s="15" t="s">
         <v>8</v>
       </c>
@@ -8200,7 +8200,7 @@
       <c r="I316" s="19"/>
       <c r="J316" s="20"/>
     </row>
-    <row r="317" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="317" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B317" s="15" t="s">
         <v>8</v>
       </c>
@@ -8223,7 +8223,7 @@
       <c r="I317" s="19"/>
       <c r="J317" s="20"/>
     </row>
-    <row r="318" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="318" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B318" s="15" t="s">
         <v>8</v>
       </c>
@@ -8246,7 +8246,7 @@
       <c r="I318" s="19"/>
       <c r="J318" s="20"/>
     </row>
-    <row r="319" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="319" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B319" s="15" t="s">
         <v>8</v>
       </c>
@@ -8269,7 +8269,7 @@
       <c r="I319" s="19"/>
       <c r="J319" s="20"/>
     </row>
-    <row r="320" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="320" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B320" s="15" t="s">
         <v>8</v>
       </c>
@@ -8292,7 +8292,7 @@
       <c r="I320" s="19"/>
       <c r="J320" s="20"/>
     </row>
-    <row r="321" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="321" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B321" s="15" t="s">
         <v>8</v>
       </c>
@@ -8315,7 +8315,7 @@
       <c r="I321" s="19"/>
       <c r="J321" s="20"/>
     </row>
-    <row r="322" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="322" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B322" s="15" t="s">
         <v>8</v>
       </c>
@@ -8338,7 +8338,7 @@
       <c r="I322" s="19"/>
       <c r="J322" s="20"/>
     </row>
-    <row r="323" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="323" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B323" s="15" t="s">
         <v>8</v>
       </c>
@@ -8361,7 +8361,7 @@
       <c r="I323" s="19"/>
       <c r="J323" s="20"/>
     </row>
-    <row r="324" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="324" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B324" s="15" t="s">
         <v>8</v>
       </c>
@@ -8384,7 +8384,7 @@
       <c r="I324" s="19"/>
       <c r="J324" s="20"/>
     </row>
-    <row r="325" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="325" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B325" s="15" t="s">
         <v>8</v>
       </c>
@@ -8407,7 +8407,7 @@
       <c r="I325" s="19"/>
       <c r="J325" s="20"/>
     </row>
-    <row r="326" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="326" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B326" s="15" t="s">
         <v>8</v>
       </c>
@@ -8430,7 +8430,7 @@
       <c r="I326" s="19"/>
       <c r="J326" s="20"/>
     </row>
-    <row r="327" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="327" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B327" s="15" t="s">
         <v>8</v>
       </c>
@@ -8453,7 +8453,7 @@
       <c r="I327" s="19"/>
       <c r="J327" s="20"/>
     </row>
-    <row r="328" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="328" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B328" s="15" t="s">
         <v>8</v>
       </c>
@@ -8476,7 +8476,7 @@
       <c r="I328" s="19"/>
       <c r="J328" s="20"/>
     </row>
-    <row r="329" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="329" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B329" s="15" t="s">
         <v>8</v>
       </c>
@@ -8499,7 +8499,7 @@
       <c r="I329" s="19"/>
       <c r="J329" s="20"/>
     </row>
-    <row r="330" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="330" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B330" s="15" t="s">
         <v>8</v>
       </c>
@@ -8522,7 +8522,7 @@
       <c r="I330" s="19"/>
       <c r="J330" s="20"/>
     </row>
-    <row r="331" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="331" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B331" s="15" t="s">
         <v>8</v>
       </c>
@@ -8545,7 +8545,7 @@
       <c r="I331" s="19"/>
       <c r="J331" s="20"/>
     </row>
-    <row r="332" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="332" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B332" s="15" t="s">
         <v>8</v>
       </c>
@@ -8568,7 +8568,7 @@
       <c r="I332" s="19"/>
       <c r="J332" s="20"/>
     </row>
-    <row r="333" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="333" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B333" s="15" t="s">
         <v>8</v>
       </c>
@@ -8591,7 +8591,7 @@
       <c r="I333" s="19"/>
       <c r="J333" s="20"/>
     </row>
-    <row r="334" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="334" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B334" s="15" t="s">
         <v>8</v>
       </c>
@@ -8614,7 +8614,7 @@
       <c r="I334" s="19"/>
       <c r="J334" s="20"/>
     </row>
-    <row r="335" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="335" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B335" s="15" t="s">
         <v>8</v>
       </c>
@@ -8637,7 +8637,7 @@
       <c r="I335" s="19"/>
       <c r="J335" s="20"/>
     </row>
-    <row r="336" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="336" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B336" s="15" t="s">
         <v>8</v>
       </c>
@@ -8660,7 +8660,7 @@
       <c r="I336" s="19"/>
       <c r="J336" s="20"/>
     </row>
-    <row r="337" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="337" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B337" s="15" t="s">
         <v>8</v>
       </c>
@@ -8683,7 +8683,7 @@
       <c r="I337" s="19"/>
       <c r="J337" s="20"/>
     </row>
-    <row r="338" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="338" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B338" s="15" t="s">
         <v>8</v>
       </c>
@@ -8706,7 +8706,7 @@
       <c r="I338" s="19"/>
       <c r="J338" s="20"/>
     </row>
-    <row r="339" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="339" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B339" s="15" t="s">
         <v>8</v>
       </c>
@@ -8729,7 +8729,7 @@
       <c r="I339" s="19"/>
       <c r="J339" s="20"/>
     </row>
-    <row r="340" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="340" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B340" s="15" t="s">
         <v>8</v>
       </c>
@@ -8752,7 +8752,7 @@
       <c r="I340" s="19"/>
       <c r="J340" s="20"/>
     </row>
-    <row r="341" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="341" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B341" s="15" t="s">
         <v>8</v>
       </c>
@@ -8775,7 +8775,7 @@
       <c r="I341" s="19"/>
       <c r="J341" s="20"/>
     </row>
-    <row r="342" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="342" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B342" s="15" t="s">
         <v>8</v>
       </c>
@@ -8798,7 +8798,7 @@
       <c r="I342" s="19"/>
       <c r="J342" s="20"/>
     </row>
-    <row r="343" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="343" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B343" s="15" t="s">
         <v>8</v>
       </c>
@@ -8821,7 +8821,7 @@
       <c r="I343" s="19"/>
       <c r="J343" s="20"/>
     </row>
-    <row r="344" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="344" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B344" s="15" t="s">
         <v>8</v>
       </c>
@@ -8844,7 +8844,7 @@
       <c r="I344" s="19"/>
       <c r="J344" s="20"/>
     </row>
-    <row r="345" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="345" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B345" s="15" t="s">
         <v>8</v>
       </c>
@@ -8867,7 +8867,7 @@
       <c r="I345" s="19"/>
       <c r="J345" s="20"/>
     </row>
-    <row r="346" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="346" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B346" s="15" t="s">
         <v>8</v>
       </c>
@@ -8890,7 +8890,7 @@
       <c r="I346" s="19"/>
       <c r="J346" s="20"/>
     </row>
-    <row r="347" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="347" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B347" s="15" t="s">
         <v>8</v>
       </c>
@@ -8913,7 +8913,7 @@
       <c r="I347" s="19"/>
       <c r="J347" s="20"/>
     </row>
-    <row r="348" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="348" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B348" s="15" t="s">
         <v>8</v>
       </c>
@@ -8936,7 +8936,7 @@
       <c r="I348" s="19"/>
       <c r="J348" s="20"/>
     </row>
-    <row r="349" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="349" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B349" s="15" t="s">
         <v>8</v>
       </c>
@@ -8959,7 +8959,7 @@
       <c r="I349" s="19"/>
       <c r="J349" s="20"/>
     </row>
-    <row r="350" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="350" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B350" s="15" t="s">
         <v>8</v>
       </c>
@@ -8982,7 +8982,7 @@
       <c r="I350" s="19"/>
       <c r="J350" s="20"/>
     </row>
-    <row r="351" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="351" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B351" s="15" t="s">
         <v>8</v>
       </c>
@@ -9005,7 +9005,7 @@
       <c r="I351" s="19"/>
       <c r="J351" s="20"/>
     </row>
-    <row r="352" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="352" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B352" s="15" t="s">
         <v>8</v>
       </c>
@@ -9028,7 +9028,7 @@
       <c r="I352" s="19"/>
       <c r="J352" s="20"/>
     </row>
-    <row r="353" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="353" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B353" s="15" t="s">
         <v>8</v>
       </c>
@@ -9051,7 +9051,7 @@
       <c r="I353" s="19"/>
       <c r="J353" s="20"/>
     </row>
-    <row r="354" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="354" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B354" s="15" t="s">
         <v>8</v>
       </c>
@@ -9074,7 +9074,7 @@
       <c r="I354" s="19"/>
       <c r="J354" s="20"/>
     </row>
-    <row r="355" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="355" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B355" s="15" t="s">
         <v>8</v>
       </c>
@@ -9097,7 +9097,7 @@
       <c r="I355" s="19"/>
       <c r="J355" s="20"/>
     </row>
-    <row r="356" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="356" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B356" s="15" t="s">
         <v>8</v>
       </c>
@@ -9120,7 +9120,7 @@
       <c r="I356" s="19"/>
       <c r="J356" s="20"/>
     </row>
-    <row r="357" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="357" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B357" s="15" t="s">
         <v>8</v>
       </c>
@@ -9143,7 +9143,7 @@
       <c r="I357" s="19"/>
       <c r="J357" s="20"/>
     </row>
-    <row r="358" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="358" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B358" s="15" t="s">
         <v>8</v>
       </c>
@@ -9166,7 +9166,7 @@
       <c r="I358" s="19"/>
       <c r="J358" s="20"/>
     </row>
-    <row r="359" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="359" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B359" s="15" t="s">
         <v>8</v>
       </c>
@@ -9189,7 +9189,7 @@
       <c r="I359" s="19"/>
       <c r="J359" s="20"/>
     </row>
-    <row r="360" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="360" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B360" s="15" t="s">
         <v>8</v>
       </c>
@@ -9212,7 +9212,7 @@
       <c r="I360" s="19"/>
       <c r="J360" s="20"/>
     </row>
-    <row r="361" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="361" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B361" s="15" t="s">
         <v>8</v>
       </c>
@@ -9235,7 +9235,7 @@
       <c r="I361" s="19"/>
       <c r="J361" s="20"/>
     </row>
-    <row r="362" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="362" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B362" s="15" t="s">
         <v>8</v>
       </c>
@@ -9258,7 +9258,7 @@
       <c r="I362" s="19"/>
       <c r="J362" s="20"/>
     </row>
-    <row r="363" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="363" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B363" s="15" t="s">
         <v>8</v>
       </c>
@@ -9281,7 +9281,7 @@
       <c r="I363" s="19"/>
       <c r="J363" s="20"/>
     </row>
-    <row r="364" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="364" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B364" s="15" t="s">
         <v>8</v>
       </c>
@@ -9304,7 +9304,7 @@
       <c r="I364" s="19"/>
       <c r="J364" s="20"/>
     </row>
-    <row r="365" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="365" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B365" s="15" t="s">
         <v>8</v>
       </c>
@@ -9327,7 +9327,7 @@
       <c r="I365" s="19"/>
       <c r="J365" s="20"/>
     </row>
-    <row r="366" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="366" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B366" s="15" t="s">
         <v>8</v>
       </c>
@@ -9350,7 +9350,7 @@
       <c r="I366" s="19"/>
       <c r="J366" s="20"/>
     </row>
-    <row r="367" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="367" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B367" s="15" t="s">
         <v>8</v>
       </c>
@@ -9373,7 +9373,7 @@
       <c r="I367" s="19"/>
       <c r="J367" s="20"/>
     </row>
-    <row r="368" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="368" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B368" s="15" t="s">
         <v>8</v>
       </c>
@@ -9396,7 +9396,7 @@
       <c r="I368" s="19"/>
       <c r="J368" s="20"/>
     </row>
-    <row r="369" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="369" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B369" s="15" t="s">
         <v>8</v>
       </c>
@@ -9419,7 +9419,7 @@
       <c r="I369" s="19"/>
       <c r="J369" s="20"/>
     </row>
-    <row r="370" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="370" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B370" s="15" t="s">
         <v>8</v>
       </c>
@@ -9442,7 +9442,7 @@
       <c r="I370" s="19"/>
       <c r="J370" s="20"/>
     </row>
-    <row r="371" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="371" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B371" s="15" t="s">
         <v>8</v>
       </c>
@@ -9465,7 +9465,7 @@
       <c r="I371" s="19"/>
       <c r="J371" s="20"/>
     </row>
-    <row r="372" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="372" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B372" s="15" t="s">
         <v>8</v>
       </c>
@@ -9488,7 +9488,7 @@
       <c r="I372" s="19"/>
       <c r="J372" s="20"/>
     </row>
-    <row r="373" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="373" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B373" s="15" t="s">
         <v>8</v>
       </c>
@@ -9511,7 +9511,7 @@
       <c r="I373" s="19"/>
       <c r="J373" s="20"/>
     </row>
-    <row r="374" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="374" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B374" s="15" t="s">
         <v>8</v>
       </c>
@@ -9534,7 +9534,7 @@
       <c r="I374" s="19"/>
       <c r="J374" s="20"/>
     </row>
-    <row r="375" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="375" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B375" s="15" t="s">
         <v>8</v>
       </c>
@@ -9557,7 +9557,7 @@
       <c r="I375" s="19"/>
       <c r="J375" s="20"/>
     </row>
-    <row r="376" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="376" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B376" s="15" t="s">
         <v>8</v>
       </c>
@@ -9580,7 +9580,7 @@
       <c r="I376" s="19"/>
       <c r="J376" s="20"/>
     </row>
-    <row r="377" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="377" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B377" s="15" t="s">
         <v>8</v>
       </c>
@@ -9603,7 +9603,7 @@
       <c r="I377" s="19"/>
       <c r="J377" s="20"/>
     </row>
-    <row r="378" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="378" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B378" s="15" t="s">
         <v>8</v>
       </c>
@@ -9626,7 +9626,7 @@
       <c r="I378" s="19"/>
       <c r="J378" s="20"/>
     </row>
-    <row r="379" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="379" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B379" s="15" t="s">
         <v>8</v>
       </c>
@@ -9649,7 +9649,7 @@
       <c r="I379" s="19"/>
       <c r="J379" s="20"/>
     </row>
-    <row r="380" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="380" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B380" s="15" t="s">
         <v>8</v>
       </c>
@@ -9672,7 +9672,7 @@
       <c r="I380" s="19"/>
       <c r="J380" s="20"/>
     </row>
-    <row r="381" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="381" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B381" s="15" t="s">
         <v>8</v>
       </c>
@@ -9695,7 +9695,7 @@
       <c r="I381" s="19"/>
       <c r="J381" s="20"/>
     </row>
-    <row r="382" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="382" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B382" s="15" t="s">
         <v>8</v>
       </c>
@@ -9718,7 +9718,7 @@
       <c r="I382" s="19"/>
       <c r="J382" s="20"/>
     </row>
-    <row r="383" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="383" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B383" s="15" t="s">
         <v>8</v>
       </c>
@@ -9741,7 +9741,7 @@
       <c r="I383" s="19"/>
       <c r="J383" s="20"/>
     </row>
-    <row r="384" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="384" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B384" s="15" t="s">
         <v>8</v>
       </c>
@@ -9764,7 +9764,7 @@
       <c r="I384" s="19"/>
       <c r="J384" s="20"/>
     </row>
-    <row r="385" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="385" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B385" s="15" t="s">
         <v>8</v>
       </c>
@@ -9787,7 +9787,7 @@
       <c r="I385" s="19"/>
       <c r="J385" s="20"/>
     </row>
-    <row r="386" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="386" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B386" s="15" t="s">
         <v>8</v>
       </c>
@@ -9810,7 +9810,7 @@
       <c r="I386" s="19"/>
       <c r="J386" s="20"/>
     </row>
-    <row r="387" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="387" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B387" s="15" t="s">
         <v>8</v>
       </c>
@@ -9833,7 +9833,7 @@
       <c r="I387" s="19"/>
       <c r="J387" s="20"/>
     </row>
-    <row r="388" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="388" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B388" s="15" t="s">
         <v>8</v>
       </c>
@@ -9856,7 +9856,7 @@
       <c r="I388" s="19"/>
       <c r="J388" s="20"/>
     </row>
-    <row r="389" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="389" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B389" s="15" t="s">
         <v>8</v>
       </c>
@@ -9879,7 +9879,7 @@
       <c r="I389" s="19"/>
       <c r="J389" s="20"/>
     </row>
-    <row r="390" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="390" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B390" s="15" t="s">
         <v>8</v>
       </c>
@@ -9902,7 +9902,7 @@
       <c r="I390" s="19"/>
       <c r="J390" s="20"/>
     </row>
-    <row r="391" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="391" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B391" s="15" t="s">
         <v>8</v>
       </c>
@@ -9925,7 +9925,7 @@
       <c r="I391" s="19"/>
       <c r="J391" s="20"/>
     </row>
-    <row r="392" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="392" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B392" s="15" t="s">
         <v>8</v>
       </c>
@@ -9948,7 +9948,7 @@
       <c r="I392" s="19"/>
       <c r="J392" s="20"/>
     </row>
-    <row r="393" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="393" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B393" s="15" t="s">
         <v>8</v>
       </c>
@@ -9971,7 +9971,7 @@
       <c r="I393" s="19"/>
       <c r="J393" s="20"/>
     </row>
-    <row r="394" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="394" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B394" s="15" t="s">
         <v>8</v>
       </c>
@@ -9994,7 +9994,7 @@
       <c r="I394" s="19"/>
       <c r="J394" s="20"/>
     </row>
-    <row r="395" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="395" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B395" s="15" t="s">
         <v>8</v>
       </c>
@@ -10017,7 +10017,7 @@
       <c r="I395" s="19"/>
       <c r="J395" s="20"/>
     </row>
-    <row r="396" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="396" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B396" s="15" t="s">
         <v>8</v>
       </c>
@@ -10040,7 +10040,7 @@
       <c r="I396" s="19"/>
       <c r="J396" s="20"/>
     </row>
-    <row r="397" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="397" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B397" s="15" t="s">
         <v>8</v>
       </c>
@@ -10063,7 +10063,7 @@
       <c r="I397" s="19"/>
       <c r="J397" s="20"/>
     </row>
-    <row r="398" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="398" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B398" s="15" t="s">
         <v>8</v>
       </c>
@@ -10086,7 +10086,7 @@
       <c r="I398" s="19"/>
       <c r="J398" s="20"/>
     </row>
-    <row r="399" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="399" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B399" s="15" t="s">
         <v>8</v>
       </c>
@@ -10109,7 +10109,7 @@
       <c r="I399" s="19"/>
       <c r="J399" s="20"/>
     </row>
-    <row r="400" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="400" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B400" s="15" t="s">
         <v>8</v>
       </c>
@@ -10132,7 +10132,7 @@
       <c r="I400" s="19"/>
       <c r="J400" s="20"/>
     </row>
-    <row r="401" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="401" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B401" s="15" t="s">
         <v>8</v>
       </c>
@@ -10155,7 +10155,7 @@
       <c r="I401" s="19"/>
       <c r="J401" s="20"/>
     </row>
-    <row r="402" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="402" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B402" s="15" t="s">
         <v>8</v>
       </c>
@@ -10178,7 +10178,7 @@
       <c r="I402" s="19"/>
       <c r="J402" s="20"/>
     </row>
-    <row r="403" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="403" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B403" s="15" t="s">
         <v>8</v>
       </c>
@@ -10201,7 +10201,7 @@
       <c r="I403" s="19"/>
       <c r="J403" s="20"/>
     </row>
-    <row r="404" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="404" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B404" s="15" t="s">
         <v>8</v>
       </c>
@@ -10224,7 +10224,7 @@
       <c r="I404" s="19"/>
       <c r="J404" s="20"/>
     </row>
-    <row r="405" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="405" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B405" s="15" t="s">
         <v>8</v>
       </c>
@@ -10247,7 +10247,7 @@
       <c r="I405" s="19"/>
       <c r="J405" s="20"/>
     </row>
-    <row r="406" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="406" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B406" s="15" t="s">
         <v>8</v>
       </c>
@@ -10270,7 +10270,7 @@
       <c r="I406" s="19"/>
       <c r="J406" s="20"/>
     </row>
-    <row r="407" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="407" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B407" s="15" t="s">
         <v>8</v>
       </c>
@@ -10293,7 +10293,7 @@
       <c r="I407" s="19"/>
       <c r="J407" s="20"/>
     </row>
-    <row r="408" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="408" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B408" s="15" t="s">
         <v>8</v>
       </c>
@@ -10316,7 +10316,7 @@
       <c r="I408" s="19"/>
       <c r="J408" s="20"/>
     </row>
-    <row r="409" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="409" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B409" s="15" t="s">
         <v>8</v>
       </c>
@@ -10339,7 +10339,7 @@
       <c r="I409" s="19"/>
       <c r="J409" s="20"/>
     </row>
-    <row r="410" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="410" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B410" s="15" t="s">
         <v>8</v>
       </c>
@@ -10362,7 +10362,7 @@
       <c r="I410" s="19"/>
       <c r="J410" s="20"/>
     </row>
-    <row r="411" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="411" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B411" s="15" t="s">
         <v>8</v>
       </c>
@@ -10385,7 +10385,7 @@
       <c r="I411" s="19"/>
       <c r="J411" s="20"/>
     </row>
-    <row r="412" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="412" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B412" s="15" t="s">
         <v>8</v>
       </c>
@@ -10408,7 +10408,7 @@
       <c r="I412" s="19"/>
       <c r="J412" s="20"/>
     </row>
-    <row r="413" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="413" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B413" s="15" t="s">
         <v>8</v>
       </c>
@@ -10431,7 +10431,7 @@
       <c r="I413" s="19"/>
       <c r="J413" s="20"/>
     </row>
-    <row r="414" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="414" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B414" s="15" t="s">
         <v>8</v>
       </c>
@@ -10454,7 +10454,7 @@
       <c r="I414" s="19"/>
       <c r="J414" s="20"/>
     </row>
-    <row r="415" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="415" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B415" s="15" t="s">
         <v>8</v>
       </c>
@@ -10477,7 +10477,7 @@
       <c r="I415" s="19"/>
       <c r="J415" s="20"/>
     </row>
-    <row r="416" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="416" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B416" s="15" t="s">
         <v>8</v>
       </c>
@@ -10500,7 +10500,7 @@
       <c r="I416" s="19"/>
       <c r="J416" s="20"/>
     </row>
-    <row r="417" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="417" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B417" s="15" t="s">
         <v>8</v>
       </c>
@@ -10523,7 +10523,7 @@
       <c r="I417" s="19"/>
       <c r="J417" s="20"/>
     </row>
-    <row r="418" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="418" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B418" s="15" t="s">
         <v>8</v>
       </c>
@@ -10546,7 +10546,7 @@
       <c r="I418" s="19"/>
       <c r="J418" s="20"/>
     </row>
-    <row r="419" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="419" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B419" s="15" t="s">
         <v>8</v>
       </c>
@@ -10569,7 +10569,7 @@
       <c r="I419" s="19"/>
       <c r="J419" s="20"/>
     </row>
-    <row r="420" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="420" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B420" s="15" t="s">
         <v>8</v>
       </c>
@@ -10592,7 +10592,7 @@
       <c r="I420" s="19"/>
       <c r="J420" s="20"/>
     </row>
-    <row r="421" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="421" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B421" s="15" t="s">
         <v>8</v>
       </c>
@@ -10615,7 +10615,7 @@
       <c r="I421" s="19"/>
       <c r="J421" s="20"/>
     </row>
-    <row r="422" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="422" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B422" s="15" t="s">
         <v>8</v>
       </c>
@@ -10638,7 +10638,7 @@
       <c r="I422" s="19"/>
       <c r="J422" s="20"/>
     </row>
-    <row r="423" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="423" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B423" s="15" t="s">
         <v>8</v>
       </c>
@@ -10661,7 +10661,7 @@
       <c r="I423" s="19"/>
       <c r="J423" s="20"/>
     </row>
-    <row r="424" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="424" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B424" s="15" t="s">
         <v>8</v>
       </c>
@@ -10684,7 +10684,7 @@
       <c r="I424" s="19"/>
       <c r="J424" s="20"/>
     </row>
-    <row r="425" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="425" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B425" s="15" t="s">
         <v>8</v>
       </c>
@@ -10707,7 +10707,7 @@
       <c r="I425" s="19"/>
       <c r="J425" s="20"/>
     </row>
-    <row r="426" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="426" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B426" s="15" t="s">
         <v>8</v>
       </c>
@@ -10730,7 +10730,7 @@
       <c r="I426" s="19"/>
       <c r="J426" s="20"/>
     </row>
-    <row r="427" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="427" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B427" s="15" t="s">
         <v>8</v>
       </c>
@@ -10753,7 +10753,7 @@
       <c r="I427" s="19"/>
       <c r="J427" s="20"/>
     </row>
-    <row r="428" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="428" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B428" s="15" t="s">
         <v>8</v>
       </c>
@@ -10776,7 +10776,7 @@
       <c r="I428" s="19"/>
       <c r="J428" s="20"/>
     </row>
-    <row r="429" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="429" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B429" s="15" t="s">
         <v>8</v>
       </c>
@@ -10799,7 +10799,7 @@
       <c r="I429" s="19"/>
       <c r="J429" s="20"/>
     </row>
-    <row r="430" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="430" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B430" s="15" t="s">
         <v>8</v>
       </c>
@@ -10822,7 +10822,7 @@
       <c r="I430" s="19"/>
       <c r="J430" s="20"/>
     </row>
-    <row r="431" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="431" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B431" s="15" t="s">
         <v>8</v>
       </c>
@@ -10845,7 +10845,7 @@
       <c r="I431" s="19"/>
       <c r="J431" s="20"/>
     </row>
-    <row r="432" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="432" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B432" s="15" t="s">
         <v>8</v>
       </c>
@@ -10868,7 +10868,7 @@
       <c r="I432" s="19"/>
       <c r="J432" s="20"/>
     </row>
-    <row r="433" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="433" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B433" s="15" t="s">
         <v>8</v>
       </c>
@@ -10891,7 +10891,7 @@
       <c r="I433" s="19"/>
       <c r="J433" s="20"/>
     </row>
-    <row r="434" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="434" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B434" s="15" t="s">
         <v>8</v>
       </c>
@@ -10914,7 +10914,7 @@
       <c r="I434" s="19"/>
       <c r="J434" s="20"/>
     </row>
-    <row r="435" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="435" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B435" s="15" t="s">
         <v>8</v>
       </c>
@@ -10937,7 +10937,7 @@
       <c r="I435" s="19"/>
       <c r="J435" s="20"/>
     </row>
-    <row r="436" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="436" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B436" s="15" t="s">
         <v>8</v>
       </c>
@@ -10960,7 +10960,7 @@
       <c r="I436" s="19"/>
       <c r="J436" s="20"/>
     </row>
-    <row r="437" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="437" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B437" s="15" t="s">
         <v>8</v>
       </c>
@@ -10983,7 +10983,7 @@
       <c r="I437" s="19"/>
       <c r="J437" s="20"/>
     </row>
-    <row r="438" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="438" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B438" s="15" t="s">
         <v>8</v>
       </c>
@@ -11006,7 +11006,7 @@
       <c r="I438" s="19"/>
       <c r="J438" s="20"/>
     </row>
-    <row r="439" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="439" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B439" s="15" t="s">
         <v>8</v>
       </c>
@@ -11029,7 +11029,7 @@
       <c r="I439" s="19"/>
       <c r="J439" s="20"/>
     </row>
-    <row r="440" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="440" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B440" s="15" t="s">
         <v>8</v>
       </c>
@@ -11052,7 +11052,7 @@
       <c r="I440" s="19"/>
       <c r="J440" s="20"/>
     </row>
-    <row r="441" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="441" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B441" s="15" t="s">
         <v>8</v>
       </c>
@@ -11075,7 +11075,7 @@
       <c r="I441" s="19"/>
       <c r="J441" s="20"/>
     </row>
-    <row r="442" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="442" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B442" s="15" t="s">
         <v>8</v>
       </c>
@@ -11098,7 +11098,7 @@
       <c r="I442" s="19"/>
       <c r="J442" s="20"/>
     </row>
-    <row r="443" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="443" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B443" s="15" t="s">
         <v>8</v>
       </c>
@@ -11121,7 +11121,7 @@
       <c r="I443" s="19"/>
       <c r="J443" s="20"/>
     </row>
-    <row r="444" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="444" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B444" s="15" t="s">
         <v>8</v>
       </c>
@@ -11144,7 +11144,7 @@
       <c r="I444" s="19"/>
       <c r="J444" s="20"/>
     </row>
-    <row r="445" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="445" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B445" s="15" t="s">
         <v>8</v>
       </c>
@@ -11167,7 +11167,7 @@
       <c r="I445" s="19"/>
       <c r="J445" s="20"/>
     </row>
-    <row r="446" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="446" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B446" s="15" t="s">
         <v>8</v>
       </c>
@@ -11190,7 +11190,7 @@
       <c r="I446" s="19"/>
       <c r="J446" s="20"/>
     </row>
-    <row r="447" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="447" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B447" s="15" t="s">
         <v>8</v>
       </c>
@@ -11213,7 +11213,7 @@
       <c r="I447" s="19"/>
       <c r="J447" s="20"/>
     </row>
-    <row r="448" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="448" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B448" s="15" t="s">
         <v>8</v>
       </c>
@@ -11236,7 +11236,7 @@
       <c r="I448" s="19"/>
       <c r="J448" s="20"/>
     </row>
-    <row r="449" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="449" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B449" s="15" t="s">
         <v>8</v>
       </c>
@@ -11259,7 +11259,7 @@
       <c r="I449" s="19"/>
       <c r="J449" s="20"/>
     </row>
-    <row r="450" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="450" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B450" s="15" t="s">
         <v>8</v>
       </c>
@@ -11282,7 +11282,7 @@
       <c r="I450" s="19"/>
       <c r="J450" s="20"/>
     </row>
-    <row r="451" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="451" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B451" s="15" t="s">
         <v>8</v>
       </c>
@@ -11305,7 +11305,7 @@
       <c r="I451" s="19"/>
       <c r="J451" s="20"/>
     </row>
-    <row r="452" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="452" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B452" s="15" t="s">
         <v>8</v>
       </c>
@@ -11328,7 +11328,7 @@
       <c r="I452" s="19"/>
       <c r="J452" s="20"/>
     </row>
-    <row r="453" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="453" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B453" s="15" t="s">
         <v>8</v>
       </c>
@@ -11351,7 +11351,7 @@
       <c r="I453" s="19"/>
       <c r="J453" s="20"/>
     </row>
-    <row r="454" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="454" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B454" s="15" t="s">
         <v>8</v>
       </c>
@@ -11374,7 +11374,7 @@
       <c r="I454" s="19"/>
       <c r="J454" s="20"/>
     </row>
-    <row r="455" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="455" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B455" s="15" t="s">
         <v>8</v>
       </c>
@@ -11397,7 +11397,7 @@
       <c r="I455" s="19"/>
       <c r="J455" s="20"/>
     </row>
-    <row r="456" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="456" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B456" s="15" t="s">
         <v>8</v>
       </c>
@@ -11420,7 +11420,7 @@
       <c r="I456" s="19"/>
       <c r="J456" s="20"/>
     </row>
-    <row r="457" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="457" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B457" s="15" t="s">
         <v>8</v>
       </c>
@@ -11443,7 +11443,7 @@
       <c r="I457" s="19"/>
       <c r="J457" s="20"/>
     </row>
-    <row r="458" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="458" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B458" s="15" t="s">
         <v>8</v>
       </c>
@@ -11466,7 +11466,7 @@
       <c r="I458" s="19"/>
       <c r="J458" s="20"/>
     </row>
-    <row r="459" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="459" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B459" s="15" t="s">
         <v>8</v>
       </c>
@@ -11489,7 +11489,7 @@
       <c r="I459" s="19"/>
       <c r="J459" s="20"/>
     </row>
-    <row r="460" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="460" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B460" s="15" t="s">
         <v>8</v>
       </c>
@@ -11512,7 +11512,7 @@
       <c r="I460" s="19"/>
       <c r="J460" s="20"/>
     </row>
-    <row r="461" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="461" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B461" s="15" t="s">
         <v>8</v>
       </c>
@@ -11535,7 +11535,7 @@
       <c r="I461" s="19"/>
       <c r="J461" s="20"/>
     </row>
-    <row r="462" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="462" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B462" s="15" t="s">
         <v>8</v>
       </c>
@@ -11558,7 +11558,7 @@
       <c r="I462" s="19"/>
       <c r="J462" s="20"/>
     </row>
-    <row r="463" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="463" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B463" s="15" t="s">
         <v>8</v>
       </c>
@@ -11581,7 +11581,7 @@
       <c r="I463" s="19"/>
       <c r="J463" s="20"/>
     </row>
-    <row r="464" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="464" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B464" s="15" t="s">
         <v>8</v>
       </c>
@@ -11604,7 +11604,7 @@
       <c r="I464" s="19"/>
       <c r="J464" s="20"/>
     </row>
-    <row r="465" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="465" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B465" s="15" t="s">
         <v>8</v>
       </c>
@@ -11627,7 +11627,7 @@
       <c r="I465" s="19"/>
       <c r="J465" s="20"/>
     </row>
-    <row r="466" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="466" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B466" s="15" t="s">
         <v>8</v>
       </c>
@@ -11650,7 +11650,7 @@
       <c r="I466" s="19"/>
       <c r="J466" s="20"/>
     </row>
-    <row r="467" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="467" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B467" s="15" t="s">
         <v>8</v>
       </c>
@@ -11673,7 +11673,7 @@
       <c r="I467" s="19"/>
       <c r="J467" s="20"/>
     </row>
-    <row r="468" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="468" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B468" s="15" t="s">
         <v>8</v>
       </c>
@@ -11696,7 +11696,7 @@
       <c r="I468" s="19"/>
       <c r="J468" s="20"/>
     </row>
-    <row r="469" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="469" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B469" s="15" t="s">
         <v>8</v>
       </c>
@@ -11719,7 +11719,7 @@
       <c r="I469" s="19"/>
       <c r="J469" s="20"/>
     </row>
-    <row r="470" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="470" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B470" s="15" t="s">
         <v>8</v>
       </c>
@@ -11742,7 +11742,7 @@
       <c r="I470" s="19"/>
       <c r="J470" s="20"/>
     </row>
-    <row r="471" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="471" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B471" s="15" t="s">
         <v>8</v>
       </c>
@@ -11765,7 +11765,7 @@
       <c r="I471" s="19"/>
       <c r="J471" s="20"/>
     </row>
-    <row r="472" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="472" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B472" s="15" t="s">
         <v>8</v>
       </c>
@@ -11788,7 +11788,7 @@
       <c r="I472" s="19"/>
       <c r="J472" s="20"/>
     </row>
-    <row r="473" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="473" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B473" s="15" t="s">
         <v>8</v>
       </c>
@@ -11811,7 +11811,7 @@
       <c r="I473" s="19"/>
       <c r="J473" s="20"/>
     </row>
-    <row r="474" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="474" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B474" s="15" t="s">
         <v>8</v>
       </c>
@@ -11834,7 +11834,7 @@
       <c r="I474" s="19"/>
       <c r="J474" s="20"/>
     </row>
-    <row r="475" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="475" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B475" s="15" t="s">
         <v>8</v>
       </c>
@@ -11857,7 +11857,7 @@
       <c r="I475" s="19"/>
       <c r="J475" s="20"/>
     </row>
-    <row r="476" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="476" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B476" s="15" t="s">
         <v>8</v>
       </c>
@@ -11880,7 +11880,7 @@
       <c r="I476" s="19"/>
       <c r="J476" s="20"/>
     </row>
-    <row r="477" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="477" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B477" s="15" t="s">
         <v>8</v>
       </c>
@@ -11903,7 +11903,7 @@
       <c r="I477" s="19"/>
       <c r="J477" s="20"/>
     </row>
-    <row r="478" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="478" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B478" s="15" t="s">
         <v>8</v>
       </c>
@@ -11926,7 +11926,7 @@
       <c r="I478" s="19"/>
       <c r="J478" s="20"/>
     </row>
-    <row r="479" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="479" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B479" s="15" t="s">
         <v>8</v>
       </c>
@@ -11949,7 +11949,7 @@
       <c r="I479" s="19"/>
       <c r="J479" s="20"/>
     </row>
-    <row r="480" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="480" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B480" s="15" t="s">
         <v>8</v>
       </c>
@@ -11972,7 +11972,7 @@
       <c r="I480" s="19"/>
       <c r="J480" s="20"/>
     </row>
-    <row r="481" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="481" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B481" s="15" t="s">
         <v>8</v>
       </c>
@@ -11995,7 +11995,7 @@
       <c r="I481" s="19"/>
       <c r="J481" s="20"/>
     </row>
-    <row r="482" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="482" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B482" s="15" t="s">
         <v>8</v>
       </c>
@@ -12018,7 +12018,7 @@
       <c r="I482" s="19"/>
       <c r="J482" s="20"/>
     </row>
-    <row r="483" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="483" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B483" s="21" t="s">
         <v>8</v>
       </c>
@@ -12041,7 +12041,7 @@
       <c r="I483" s="25"/>
       <c r="J483" s="26"/>
     </row>
-    <row r="488" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="488" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B488" s="32" t="s">
         <v>114</v>
       </c>
@@ -12052,7 +12052,7 @@
       <c r="I488" s="1"/>
       <c r="J488" s="1"/>
     </row>
-    <row r="489" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="489" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B489" s="32" t="s">
         <v>113</v>
       </c>
